--- a/backend/data/financials_by_company/1202.SR.xlsx
+++ b/backend/data/financials_by_company/1202.SR.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,626 +682,784 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-4142802.6</v>
+        <v>58697.034123</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2</v>
+        <v>0.030539</v>
       </c>
       <c r="D2" t="n">
-        <v>109970745</v>
+        <v>338234668</v>
       </c>
       <c r="E2" t="n">
-        <v>-20714013</v>
+        <v>1922048</v>
       </c>
       <c r="F2" t="n">
-        <v>-20714013</v>
+        <v>1922048</v>
       </c>
       <c r="G2" t="n">
-        <v>-77326129</v>
+        <v>220710095</v>
       </c>
       <c r="H2" t="n">
-        <v>113679014</v>
+        <v>99211038</v>
       </c>
       <c r="I2" t="n">
-        <v>957629091</v>
+        <v>663297385</v>
       </c>
       <c r="J2" t="n">
-        <v>89256732</v>
+        <v>340156716</v>
       </c>
       <c r="K2" t="n">
-        <v>-24422282</v>
+        <v>240945678</v>
       </c>
       <c r="L2" t="n">
-        <v>-6575724</v>
+        <v>-15804002</v>
       </c>
       <c r="M2" t="n">
-        <v>33477733</v>
-      </c>
-      <c r="N2" t="n">
-        <v>30813689</v>
-      </c>
+        <v>13121545</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>-60754918.6</v>
+        <v>218846744.034123</v>
       </c>
       <c r="P2" t="n">
-        <v>-77326129</v>
+        <v>220710095</v>
       </c>
       <c r="Q2" t="n">
-        <v>1093790109</v>
+        <v>814864915</v>
       </c>
       <c r="R2" t="n">
-        <v>1496465</v>
+        <v>1500557</v>
       </c>
       <c r="S2" t="n">
-        <v>-52532671</v>
+        <v>242317938</v>
       </c>
       <c r="T2" t="n">
-        <v>86502282</v>
+        <v>66616667</v>
       </c>
       <c r="U2" t="n">
-        <v>86502282</v>
+        <v>66616667</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.89</v>
+        <v>3.31</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.89</v>
+        <v>3.31</v>
       </c>
       <c r="X2" t="n">
-        <v>-77326129</v>
+        <v>220710095</v>
       </c>
       <c r="Y2" t="n">
-        <v>-77326129</v>
+        <v>220710095</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-77326129</v>
+        <v>220710095</v>
       </c>
       <c r="AB2" t="n">
-        <v>141871</v>
+        <v>-156563</v>
       </c>
       <c r="AC2" t="n">
-        <v>-77468000</v>
+        <v>220866658</v>
       </c>
       <c r="AD2" t="n">
-        <v>-77468000</v>
+        <v>220866658</v>
       </c>
       <c r="AE2" t="n">
-        <v>19567985</v>
+        <v>6957475</v>
       </c>
       <c r="AF2" t="n">
-        <v>-57900015</v>
+        <v>227824133</v>
       </c>
       <c r="AG2" t="n">
-        <v>-20714013</v>
+        <v>1825092</v>
       </c>
       <c r="AH2" t="n">
-        <v>-3230730</v>
+        <v>-11494157</v>
       </c>
       <c r="AI2" t="n">
-        <v>7401311</v>
+        <v>8631766</v>
       </c>
       <c r="AJ2" t="n">
-        <v>16543432</v>
+        <v>1037299</v>
       </c>
       <c r="AK2" t="n">
-        <v>-6575724</v>
+        <v>-15804002</v>
       </c>
       <c r="AL2" t="n">
-        <v>3911680</v>
+        <v>2682457</v>
       </c>
       <c r="AM2" t="n">
-        <v>33477733</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>30813689</v>
-      </c>
+        <v>13121545</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>-28534148</v>
+        <v>242534715</v>
       </c>
       <c r="AP2" t="n">
-        <v>136161018</v>
+        <v>151567530</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5532331</v>
+        <v>783687</v>
       </c>
       <c r="AR2" t="n">
-        <v>4799497</v>
+        <v>2237657</v>
       </c>
       <c r="AS2" t="n">
-        <v>4799497</v>
+        <v>2237657</v>
       </c>
       <c r="AT2" t="n">
-        <v>42245618</v>
+        <v>88879692</v>
       </c>
       <c r="AU2" t="n">
-        <v>9812437</v>
+        <v>73483650</v>
       </c>
       <c r="AV2" t="n">
-        <v>32433181</v>
+        <v>15396042</v>
       </c>
       <c r="AW2" t="n">
-        <v>107626870</v>
+        <v>394102245</v>
       </c>
       <c r="AX2" t="n">
-        <v>957629091</v>
+        <v>663297385</v>
       </c>
       <c r="AY2" t="n">
-        <v>1065255961</v>
+        <v>1057399630</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1065255961</v>
+        <v>1057399630</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>1176899.4</v>
+        <v>-994681.757276</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2</v>
+        <v>0.052767</v>
       </c>
       <c r="D3" t="n">
-        <v>45151947</v>
+        <v>422270307</v>
       </c>
       <c r="E3" t="n">
-        <v>5884497</v>
+        <v>-18850372</v>
       </c>
       <c r="F3" t="n">
-        <v>5884497</v>
+        <v>-18850372</v>
       </c>
       <c r="G3" t="n">
-        <v>-80269141</v>
+        <v>269698532</v>
       </c>
       <c r="H3" t="n">
-        <v>103128427</v>
+        <v>100368813</v>
       </c>
       <c r="I3" t="n">
-        <v>823076340</v>
+        <v>684219701</v>
       </c>
       <c r="J3" t="n">
-        <v>51036444</v>
+        <v>403419935</v>
       </c>
       <c r="K3" t="n">
-        <v>-52091983</v>
+        <v>303051122</v>
       </c>
       <c r="L3" t="n">
-        <v>-28324186</v>
+        <v>-21028249</v>
       </c>
       <c r="M3" t="n">
-        <v>25666983</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
+        <v>17239845</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>-84976738.59999999</v>
+        <v>287554222.242724</v>
       </c>
       <c r="P3" t="n">
-        <v>-80269141</v>
+        <v>269698532</v>
       </c>
       <c r="Q3" t="n">
-        <v>924640239</v>
+        <v>857182850</v>
       </c>
       <c r="R3" t="n">
-        <v>2006552</v>
+        <v>1235509</v>
       </c>
       <c r="S3" t="n">
-        <v>-51234467</v>
+        <v>304294383</v>
       </c>
       <c r="T3" t="n">
-        <v>66666666</v>
+        <v>66666438</v>
       </c>
       <c r="U3" t="n">
-        <v>66666666</v>
+        <v>66666438</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2</v>
+        <v>4.05</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.2</v>
+        <v>4.05</v>
       </c>
       <c r="X3" t="n">
-        <v>-80269141</v>
+        <v>269698532</v>
       </c>
       <c r="Y3" t="n">
-        <v>-80269141</v>
+        <v>269698532</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-80269141</v>
+        <v>269698532</v>
       </c>
       <c r="AB3" t="n">
-        <v>7368356</v>
+        <v>-1031278</v>
       </c>
       <c r="AC3" t="n">
-        <v>-87637497</v>
+        <v>270729810</v>
       </c>
       <c r="AD3" t="n">
-        <v>-87637497</v>
+        <v>270729810</v>
       </c>
       <c r="AE3" t="n">
-        <v>9878531</v>
+        <v>15081467</v>
       </c>
       <c r="AF3" t="n">
-        <v>-77758966</v>
+        <v>285811277</v>
       </c>
       <c r="AG3" t="n">
-        <v>5884497</v>
+        <v>-18850372</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1382781</v>
+        <v>2134071</v>
       </c>
       <c r="AI3" t="n">
-        <v>-6657591</v>
+        <v>16283851</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2155875</v>
+        <v>432450</v>
       </c>
       <c r="AK3" t="n">
-        <v>-28324186</v>
+        <v>-21028249</v>
       </c>
       <c r="AL3" t="n">
-        <v>2657203</v>
+        <v>3788404</v>
       </c>
       <c r="AM3" t="n">
-        <v>25666983</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
+        <v>17239845</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>-57887468</v>
+        <v>329822948</v>
       </c>
       <c r="AP3" t="n">
-        <v>101563899</v>
+        <v>172963149</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1214032</v>
+        <v>732489</v>
       </c>
       <c r="AR3" t="n">
-        <v>4565739</v>
+        <v>4211330</v>
       </c>
       <c r="AS3" t="n">
-        <v>4565739</v>
+        <v>4211330</v>
       </c>
       <c r="AT3" t="n">
-        <v>26806437</v>
+        <v>100917365</v>
       </c>
       <c r="AU3" t="n">
-        <v>9769603</v>
+        <v>74908682</v>
       </c>
       <c r="AV3" t="n">
-        <v>17036834</v>
+        <v>26008683</v>
       </c>
       <c r="AW3" t="n">
-        <v>43676431</v>
+        <v>502786097</v>
       </c>
       <c r="AX3" t="n">
-        <v>823076340</v>
+        <v>684219701</v>
       </c>
       <c r="AY3" t="n">
-        <v>866752771</v>
+        <v>1187005798</v>
       </c>
       <c r="AZ3" t="n">
-        <v>866752771</v>
+        <v>1187005798</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-994681.757276</v>
+        <v>1176899.4</v>
       </c>
       <c r="C4" t="n">
-        <v>0.052767</v>
+        <v>0.2</v>
       </c>
       <c r="D4" t="n">
-        <v>422270307</v>
+        <v>45151947</v>
       </c>
       <c r="E4" t="n">
-        <v>-18850372</v>
+        <v>5884497</v>
       </c>
       <c r="F4" t="n">
-        <v>-18850372</v>
+        <v>5884497</v>
       </c>
       <c r="G4" t="n">
-        <v>269698532</v>
+        <v>-80269141</v>
       </c>
       <c r="H4" t="n">
-        <v>100368813</v>
+        <v>103128427</v>
       </c>
       <c r="I4" t="n">
-        <v>684219701</v>
+        <v>823076340</v>
       </c>
       <c r="J4" t="n">
-        <v>403419935</v>
+        <v>51036444</v>
       </c>
       <c r="K4" t="n">
-        <v>303051122</v>
+        <v>-52091983</v>
       </c>
       <c r="L4" t="n">
-        <v>-21028249</v>
+        <v>-28324186</v>
       </c>
       <c r="M4" t="n">
-        <v>17239845</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
+        <v>25666983</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
       <c r="O4" t="n">
-        <v>287554222.242724</v>
+        <v>-84976738.59999999</v>
       </c>
       <c r="P4" t="n">
-        <v>269698532</v>
+        <v>-80269141</v>
       </c>
       <c r="Q4" t="n">
-        <v>857182850</v>
+        <v>924640239</v>
       </c>
       <c r="R4" t="n">
-        <v>1235509</v>
+        <v>2006552</v>
       </c>
       <c r="S4" t="n">
-        <v>304294383</v>
+        <v>-51234467</v>
       </c>
       <c r="T4" t="n">
-        <v>66666438</v>
+        <v>66666666</v>
       </c>
       <c r="U4" t="n">
-        <v>66666438</v>
+        <v>66666666</v>
       </c>
       <c r="V4" t="n">
-        <v>4.05</v>
+        <v>-1.2</v>
       </c>
       <c r="W4" t="n">
-        <v>4.05</v>
+        <v>-1.2</v>
       </c>
       <c r="X4" t="n">
-        <v>269698532</v>
+        <v>-80269141</v>
       </c>
       <c r="Y4" t="n">
-        <v>269698532</v>
+        <v>-80269141</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>269698532</v>
+        <v>-80269141</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1031278</v>
+        <v>7368356</v>
       </c>
       <c r="AC4" t="n">
-        <v>270729810</v>
+        <v>-87637497</v>
       </c>
       <c r="AD4" t="n">
-        <v>270729810</v>
+        <v>-87637497</v>
       </c>
       <c r="AE4" t="n">
-        <v>15081467</v>
+        <v>9878531</v>
       </c>
       <c r="AF4" t="n">
-        <v>285811277</v>
+        <v>-77758966</v>
       </c>
       <c r="AG4" t="n">
-        <v>-18850372</v>
+        <v>5884497</v>
       </c>
       <c r="AH4" t="n">
-        <v>2134071</v>
+        <v>-1382781</v>
       </c>
       <c r="AI4" t="n">
-        <v>16283851</v>
+        <v>-6657591</v>
       </c>
       <c r="AJ4" t="n">
-        <v>432450</v>
+        <v>2155875</v>
       </c>
       <c r="AK4" t="n">
-        <v>-21028249</v>
+        <v>-28324186</v>
       </c>
       <c r="AL4" t="n">
-        <v>3788404</v>
+        <v>2657203</v>
       </c>
       <c r="AM4" t="n">
-        <v>17239845</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
+        <v>25666983</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
       <c r="AO4" t="n">
-        <v>329822948</v>
+        <v>-57887468</v>
       </c>
       <c r="AP4" t="n">
-        <v>172963149</v>
+        <v>101563899</v>
       </c>
       <c r="AQ4" t="n">
-        <v>732489</v>
+        <v>1214032</v>
       </c>
       <c r="AR4" t="n">
-        <v>4211330</v>
+        <v>4565739</v>
       </c>
       <c r="AS4" t="n">
-        <v>4211330</v>
+        <v>4565739</v>
       </c>
       <c r="AT4" t="n">
-        <v>100917365</v>
+        <v>26806437</v>
       </c>
       <c r="AU4" t="n">
-        <v>75969649</v>
+        <v>7934124</v>
       </c>
       <c r="AV4" t="n">
-        <v>24947716</v>
+        <v>18872313</v>
       </c>
       <c r="AW4" t="n">
-        <v>502786097</v>
+        <v>43676431</v>
       </c>
       <c r="AX4" t="n">
-        <v>684219701</v>
+        <v>823076340</v>
       </c>
       <c r="AY4" t="n">
-        <v>1187005798</v>
+        <v>866752771</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1187005798</v>
+        <v>866752771</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>58697.034123</v>
+        <v>-4142802.6</v>
       </c>
       <c r="C5" t="n">
-        <v>0.030539</v>
+        <v>0.2</v>
       </c>
       <c r="D5" t="n">
-        <v>338234668</v>
+        <v>109970745</v>
       </c>
       <c r="E5" t="n">
-        <v>1922048</v>
+        <v>-20714013</v>
       </c>
       <c r="F5" t="n">
-        <v>1922048</v>
+        <v>-20714013</v>
       </c>
       <c r="G5" t="n">
-        <v>220710095</v>
+        <v>-77326129</v>
       </c>
       <c r="H5" t="n">
-        <v>99211038</v>
+        <v>113679014</v>
       </c>
       <c r="I5" t="n">
-        <v>663297385</v>
+        <v>957629091</v>
       </c>
       <c r="J5" t="n">
-        <v>340156716</v>
+        <v>89256732</v>
       </c>
       <c r="K5" t="n">
-        <v>240945678</v>
+        <v>-24422282</v>
       </c>
       <c r="L5" t="n">
-        <v>-15804002</v>
+        <v>-6575724</v>
       </c>
       <c r="M5" t="n">
-        <v>13121545</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
+        <v>33477733</v>
+      </c>
+      <c r="N5" t="n">
+        <v>30813689</v>
+      </c>
       <c r="O5" t="n">
-        <v>218846744.034123</v>
+        <v>-60754918.6</v>
       </c>
       <c r="P5" t="n">
-        <v>220710095</v>
+        <v>-77326129</v>
       </c>
       <c r="Q5" t="n">
-        <v>814864915</v>
+        <v>1093790109</v>
       </c>
       <c r="R5" t="n">
-        <v>1500557</v>
+        <v>2046028</v>
       </c>
       <c r="S5" t="n">
-        <v>242317938</v>
+        <v>-52532671</v>
       </c>
       <c r="T5" t="n">
-        <v>66616667</v>
+        <v>86502282</v>
       </c>
       <c r="U5" t="n">
-        <v>66616667</v>
+        <v>86502282</v>
       </c>
       <c r="V5" t="n">
-        <v>3.31</v>
+        <v>-0.89</v>
       </c>
       <c r="W5" t="n">
-        <v>3.31</v>
+        <v>-0.89</v>
       </c>
       <c r="X5" t="n">
-        <v>220710095</v>
+        <v>-77326129</v>
       </c>
       <c r="Y5" t="n">
-        <v>220710095</v>
+        <v>-77326129</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>220710095</v>
+        <v>-77326129</v>
       </c>
       <c r="AB5" t="n">
-        <v>-156563</v>
+        <v>141871</v>
       </c>
       <c r="AC5" t="n">
-        <v>220866658</v>
+        <v>-77468000</v>
       </c>
       <c r="AD5" t="n">
-        <v>220866658</v>
+        <v>-77468000</v>
       </c>
       <c r="AE5" t="n">
-        <v>6957475</v>
+        <v>19567985</v>
       </c>
       <c r="AF5" t="n">
-        <v>227824133</v>
+        <v>-57900015</v>
       </c>
       <c r="AG5" t="n">
-        <v>1825092</v>
+        <v>-20714013</v>
       </c>
       <c r="AH5" t="n">
-        <v>-11494157</v>
+        <v>-3230730</v>
       </c>
       <c r="AI5" t="n">
-        <v>8631766</v>
+        <v>7401311</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1037299</v>
+        <v>16543432</v>
       </c>
       <c r="AK5" t="n">
-        <v>-15804002</v>
+        <v>-6575724</v>
       </c>
       <c r="AL5" t="n">
-        <v>2682457</v>
+        <v>3911680</v>
       </c>
       <c r="AM5" t="n">
-        <v>13121545</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
+        <v>33477733</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>30813689</v>
+      </c>
       <c r="AO5" t="n">
-        <v>242534715</v>
+        <v>-28534148</v>
       </c>
       <c r="AP5" t="n">
-        <v>151567530</v>
+        <v>136161018</v>
       </c>
       <c r="AQ5" t="n">
-        <v>783687</v>
+        <v>2740661</v>
       </c>
       <c r="AR5" t="n">
-        <v>2237657</v>
+        <v>4804396</v>
       </c>
       <c r="AS5" t="n">
-        <v>2237657</v>
+        <v>4804396</v>
       </c>
       <c r="AT5" t="n">
-        <v>88879692</v>
+        <v>43998074</v>
       </c>
       <c r="AU5" t="n">
-        <v>73483650</v>
+        <v>8692338</v>
       </c>
       <c r="AV5" t="n">
-        <v>15396042</v>
+        <v>35305736</v>
       </c>
       <c r="AW5" t="n">
-        <v>394102245</v>
+        <v>107626870</v>
       </c>
       <c r="AX5" t="n">
-        <v>663297385</v>
+        <v>957629091</v>
       </c>
       <c r="AY5" t="n">
-        <v>1057399630</v>
+        <v>1065255961</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1057399630</v>
+        <v>1065255961</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3859266.587092</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.376996</v>
+      </c>
+      <c r="D6" t="n">
+        <v>180304069</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10236901</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10236901</v>
+      </c>
+      <c r="G6" t="n">
+        <v>23410074</v>
+      </c>
+      <c r="H6" t="n">
+        <v>121348031</v>
+      </c>
+      <c r="I6" t="n">
+        <v>926909015</v>
+      </c>
+      <c r="J6" t="n">
+        <v>190540970</v>
+      </c>
+      <c r="K6" t="n">
+        <v>69192939</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-10245185</v>
+      </c>
+      <c r="M6" t="n">
+        <v>33553512</v>
+      </c>
+      <c r="N6" t="n">
+        <v>26430531</v>
+      </c>
+      <c r="O6" t="n">
+        <v>17032439.587092</v>
+      </c>
+      <c r="P6" t="n">
+        <v>23410074</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1023990452</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3919837</v>
+      </c>
+      <c r="S6" t="n">
+        <v>44967159</v>
+      </c>
+      <c r="T6" t="n">
+        <v>86666666</v>
+      </c>
+      <c r="U6" t="n">
+        <v>86666666</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="X6" t="n">
+        <v>23410074</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>23410074</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>23410074</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1206554</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>22203520</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>22203520</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>13435907</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>35639427</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>10236901</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-6141397</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-4095504</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-10245185</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>3122204</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>33553512</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>26430531</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>36536812</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>97081437</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>2400603</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>6779069</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>6779069</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>35685731</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6151262</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>29534469</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>133618249</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>926909015</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1060527264</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1060527264</v>
       </c>
     </row>
   </sheetData>
@@ -1315,7 +1473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS5"/>
+  <dimension ref="A1:BS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1672,260 +1830,152 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="n">
-        <v>86666665</v>
-      </c>
-      <c r="D2" t="n">
-        <v>86666665</v>
-      </c>
-      <c r="E2" t="n">
-        <v>80460087</v>
-      </c>
-      <c r="F2" t="n">
-        <v>708929299</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1585081272</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2297370899</v>
-      </c>
-      <c r="I2" t="n">
-        <v>612999530</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1585081272</v>
-      </c>
-      <c r="K2" t="n">
-        <v>17786093</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1606227693</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1857380297</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1600033352</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-6194341</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1606227693</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>184282212</v>
-      </c>
-      <c r="T2" t="n">
-        <v>419999979</v>
-      </c>
-      <c r="U2" t="n">
-        <v>866666650</v>
-      </c>
-      <c r="V2" t="n">
-        <v>866666650</v>
-      </c>
-      <c r="W2" t="n">
-        <v>958566909</v>
-      </c>
-      <c r="X2" t="n">
-        <v>302813464</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>41452198</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>261361266</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>10208662</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>251152604</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>655753445</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="n">
+        <v>399999</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>1715000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1136135</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="n">
-        <v>19910229</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>447568033</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>7577431</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>439990602</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>21114766</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>152497805</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>6532570</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1316353</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>144648882</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>2558600261</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1289847286</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>21146421</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>21146421</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1268700865</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>-1163775276</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2432476141</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>27621024</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="n">
-        <v>1959175041</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>289554245</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>156125831</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1268752975</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="n">
-        <v>130807653</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>186367314</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>-34432090</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>51497074</v>
-      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="n">
+        <v>973205206</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="n">
+        <v>86799480</v>
+      </c>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>169302330</v>
-      </c>
+        <v>2660375</v>
+      </c>
+      <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="n">
-        <v>2553204</v>
+        <v>1923363</v>
       </c>
       <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="n">
-        <v>338341685</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>-27586026</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>365927711</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>610683119</v>
-      </c>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="n">
-        <v>610683119</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>310629751</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>300053368</v>
-      </c>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="n">
+        <v>5633</v>
+      </c>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>66666666</v>
+        <v>66670000</v>
       </c>
       <c r="D3" t="n">
-        <v>66666666</v>
+        <v>66670000</v>
       </c>
       <c r="E3" t="n">
-        <v>510339552</v>
+        <v>399474045</v>
       </c>
       <c r="F3" t="n">
-        <v>591794506</v>
+        <v>574149966</v>
       </c>
       <c r="G3" t="n">
-        <v>1073965966</v>
+        <v>1180780589</v>
       </c>
       <c r="H3" t="n">
-        <v>1641179759</v>
+        <v>1725768407</v>
       </c>
       <c r="I3" t="n">
-        <v>172724033</v>
+        <v>529195757</v>
       </c>
       <c r="J3" t="n">
-        <v>1073965966</v>
+        <v>1180780589</v>
       </c>
       <c r="K3" t="n">
-        <v>24905561</v>
+        <v>29429840</v>
       </c>
       <c r="L3" t="n">
-        <v>1074290814</v>
+        <v>1181048281</v>
       </c>
       <c r="M3" t="n">
-        <v>1424495316</v>
+        <v>1592375704</v>
       </c>
       <c r="N3" t="n">
-        <v>1068203410</v>
+        <v>1182286122</v>
       </c>
       <c r="O3" t="n">
-        <v>-6087404</v>
+        <v>1237841</v>
       </c>
       <c r="P3" t="n">
-        <v>1074290814</v>
+        <v>1181048281</v>
       </c>
       <c r="Q3" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
+        <v>7860000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
       <c r="S3" t="n">
-        <v>261845302</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
+        <v>371242769</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
         <v>666666660</v>
       </c>
@@ -1933,206 +1983,198 @@
         <v>666666660</v>
       </c>
       <c r="W3" t="n">
-        <v>862730540</v>
+        <v>764228251</v>
       </c>
       <c r="X3" t="n">
-        <v>415625364</v>
+        <v>481341279</v>
       </c>
       <c r="Y3" t="n">
-        <v>48808117</v>
+        <v>48014426</v>
       </c>
       <c r="Z3" t="n">
-        <v>366817247</v>
+        <v>433326853</v>
       </c>
       <c r="AA3" t="n">
-        <v>16612745</v>
+        <v>21999430</v>
       </c>
       <c r="AB3" t="n">
-        <v>350204502</v>
+        <v>411327423</v>
       </c>
       <c r="AC3" t="n">
-        <v>447105176</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>7090840</v>
-      </c>
+        <v>282886972</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>9728580</v>
+        <v>13386571</v>
       </c>
       <c r="AF3" t="n">
-        <v>224977259</v>
+        <v>140823113</v>
       </c>
       <c r="AG3" t="n">
-        <v>8292816</v>
+        <v>7430410</v>
       </c>
       <c r="AH3" t="n">
-        <v>216684443</v>
+        <v>133392703</v>
       </c>
       <c r="AI3" t="n">
-        <v>22648954</v>
+        <v>33813502</v>
       </c>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
-        <v>173308773</v>
+        <v>88302166</v>
       </c>
       <c r="AL3" t="n">
-        <v>6653931</v>
+        <v>6087249</v>
       </c>
       <c r="AM3" t="n">
-        <v>1809818</v>
+        <v>119016</v>
       </c>
       <c r="AN3" t="n">
-        <v>164845024</v>
+        <v>82095901</v>
       </c>
       <c r="AO3" t="n">
-        <v>1930933950</v>
+        <v>1946514373</v>
       </c>
       <c r="AP3" t="n">
-        <v>1311104741</v>
+        <v>1134431644</v>
       </c>
       <c r="AQ3" t="n">
-        <v>324848</v>
+        <v>267692</v>
       </c>
       <c r="AR3" t="n">
-        <v>324848</v>
+        <v>267692</v>
       </c>
       <c r="AS3" t="n">
-        <v>1310779893</v>
+        <v>1134163952</v>
       </c>
       <c r="AT3" t="n">
-        <v>-1169419868</v>
+        <v>-1108469167</v>
       </c>
       <c r="AU3" t="n">
-        <v>2480199761</v>
+        <v>2242633119</v>
       </c>
       <c r="AV3" t="n">
-        <v>171234329</v>
+        <v>233703635</v>
       </c>
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>1886298758</v>
+        <v>1625160236</v>
       </c>
       <c r="AY3" t="n">
-        <v>260721182</v>
+        <v>198342349</v>
       </c>
       <c r="AZ3" t="n">
-        <v>161945492</v>
+        <v>185426899</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>619829209</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>10000000</v>
-      </c>
+        <v>812082729</v>
+      </c>
+      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
-        <v>110252480</v>
+        <v>153636418</v>
       </c>
       <c r="BE3" t="n">
-        <v>175697378</v>
+        <v>212777017</v>
       </c>
       <c r="BF3" t="n">
-        <v>-9602363</v>
+        <v>-6103970</v>
       </c>
       <c r="BG3" t="n">
-        <v>55526349</v>
+        <v>55105332</v>
       </c>
       <c r="BH3" t="n">
-        <v>1877813</v>
+        <v>2679115</v>
       </c>
       <c r="BI3" t="n">
-        <v>127895579</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>987645</v>
-      </c>
+        <v>161096540</v>
+      </c>
+      <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="n">
-        <v>98344</v>
+        <v>2680845</v>
       </c>
       <c r="BL3" t="n">
-        <v>266336680</v>
+        <v>297736735</v>
       </c>
       <c r="BM3" t="n">
-        <v>-22441070</v>
+        <v>-31210419</v>
       </c>
       <c r="BN3" t="n">
-        <v>288777750</v>
+        <v>328947154</v>
       </c>
       <c r="BO3" t="n">
-        <v>56555026</v>
+        <v>145251714</v>
       </c>
       <c r="BP3" t="n">
         <v>5633</v>
       </c>
       <c r="BQ3" t="n">
-        <v>56549393</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>0</v>
-      </c>
+        <v>145246081</v>
+      </c>
+      <c r="BR3" t="inlineStr"/>
       <c r="BS3" t="n">
-        <v>56549393</v>
+        <v>145246081</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>66670000</v>
+        <v>66666666</v>
       </c>
       <c r="D4" t="n">
-        <v>66670000</v>
+        <v>66666666</v>
       </c>
       <c r="E4" t="n">
-        <v>399474045</v>
+        <v>510339552</v>
       </c>
       <c r="F4" t="n">
-        <v>574149966</v>
+        <v>591794506</v>
       </c>
       <c r="G4" t="n">
-        <v>1180780589</v>
+        <v>1073965966</v>
       </c>
       <c r="H4" t="n">
-        <v>1725768407</v>
+        <v>1641179759</v>
       </c>
       <c r="I4" t="n">
-        <v>529195757</v>
+        <v>172724033</v>
       </c>
       <c r="J4" t="n">
-        <v>1180780589</v>
+        <v>1073965966</v>
       </c>
       <c r="K4" t="n">
-        <v>29429840</v>
+        <v>24905561</v>
       </c>
       <c r="L4" t="n">
-        <v>1181048281</v>
+        <v>1074290814</v>
       </c>
       <c r="M4" t="n">
-        <v>1592375704</v>
+        <v>1424495316</v>
       </c>
       <c r="N4" t="n">
-        <v>1182286122</v>
+        <v>1068203410</v>
       </c>
       <c r="O4" t="n">
-        <v>1237841</v>
+        <v>-6087404</v>
       </c>
       <c r="P4" t="n">
-        <v>1181048281</v>
+        <v>1074290814</v>
       </c>
       <c r="Q4" t="n">
-        <v>7860000</v>
-      </c>
-      <c r="R4" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>261845302</v>
+      </c>
+      <c r="T4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="n">
-        <v>371242769</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
         <v>666666660</v>
       </c>
@@ -2140,346 +2182,545 @@
         <v>666666660</v>
       </c>
       <c r="W4" t="n">
-        <v>764228251</v>
+        <v>862730540</v>
       </c>
       <c r="X4" t="n">
-        <v>481341279</v>
+        <v>415625364</v>
       </c>
       <c r="Y4" t="n">
-        <v>48014426</v>
+        <v>48808117</v>
       </c>
       <c r="Z4" t="n">
-        <v>433326853</v>
+        <v>366817247</v>
       </c>
       <c r="AA4" t="n">
-        <v>21999430</v>
+        <v>16612745</v>
       </c>
       <c r="AB4" t="n">
-        <v>411327423</v>
+        <v>350204502</v>
       </c>
       <c r="AC4" t="n">
-        <v>282886972</v>
-      </c>
-      <c r="AD4" t="inlineStr"/>
+        <v>447105176</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>7090840</v>
+      </c>
       <c r="AE4" t="n">
-        <v>13386571</v>
+        <v>9728580</v>
       </c>
       <c r="AF4" t="n">
-        <v>140823113</v>
+        <v>224977259</v>
       </c>
       <c r="AG4" t="n">
-        <v>7430410</v>
+        <v>8292816</v>
       </c>
       <c r="AH4" t="n">
-        <v>133392703</v>
+        <v>216684443</v>
       </c>
       <c r="AI4" t="n">
-        <v>33813502</v>
+        <v>22648954</v>
       </c>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>88302166</v>
+        <v>173308773</v>
       </c>
       <c r="AL4" t="n">
-        <v>6087249</v>
+        <v>6653931</v>
       </c>
       <c r="AM4" t="n">
-        <v>119016</v>
+        <v>1809818</v>
       </c>
       <c r="AN4" t="n">
-        <v>82095901</v>
+        <v>164845024</v>
       </c>
       <c r="AO4" t="n">
-        <v>1946514373</v>
+        <v>1930933950</v>
       </c>
       <c r="AP4" t="n">
-        <v>1134431644</v>
+        <v>1311104741</v>
       </c>
       <c r="AQ4" t="n">
-        <v>267692</v>
+        <v>324848</v>
       </c>
       <c r="AR4" t="n">
-        <v>267692</v>
+        <v>324848</v>
       </c>
       <c r="AS4" t="n">
-        <v>1134163952</v>
+        <v>1310779893</v>
       </c>
       <c r="AT4" t="n">
-        <v>-1108469167</v>
+        <v>-1169419868</v>
       </c>
       <c r="AU4" t="n">
-        <v>2242633119</v>
+        <v>2480199761</v>
       </c>
       <c r="AV4" t="n">
-        <v>233703635</v>
+        <v>171234329</v>
       </c>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>1625160236</v>
+        <v>1886298758</v>
       </c>
       <c r="AY4" t="n">
-        <v>198342349</v>
+        <v>260721182</v>
       </c>
       <c r="AZ4" t="n">
-        <v>185426899</v>
+        <v>161945492</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>812082729</v>
-      </c>
-      <c r="BC4" t="inlineStr"/>
+        <v>619829209</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>10000000</v>
+      </c>
       <c r="BD4" t="n">
-        <v>153636418</v>
+        <v>110252480</v>
       </c>
       <c r="BE4" t="n">
-        <v>212777017</v>
+        <v>175697378</v>
       </c>
       <c r="BF4" t="n">
-        <v>-6103970</v>
+        <v>-9602363</v>
       </c>
       <c r="BG4" t="n">
-        <v>55105332</v>
+        <v>55526349</v>
       </c>
       <c r="BH4" t="n">
-        <v>2679115</v>
+        <v>1877813</v>
       </c>
       <c r="BI4" t="n">
-        <v>161096540</v>
-      </c>
-      <c r="BJ4" t="inlineStr"/>
+        <v>127895579</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>987645</v>
+      </c>
       <c r="BK4" t="n">
-        <v>2680845</v>
+        <v>98344</v>
       </c>
       <c r="BL4" t="n">
-        <v>297736735</v>
+        <v>266336680</v>
       </c>
       <c r="BM4" t="n">
-        <v>-31210419</v>
+        <v>-22441070</v>
       </c>
       <c r="BN4" t="n">
-        <v>328947154</v>
+        <v>288777750</v>
       </c>
       <c r="BO4" t="n">
-        <v>145251714</v>
+        <v>56555026</v>
       </c>
       <c r="BP4" t="n">
         <v>5633</v>
       </c>
       <c r="BQ4" t="n">
-        <v>145246081</v>
-      </c>
-      <c r="BR4" t="inlineStr"/>
+        <v>56549393</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0</v>
+      </c>
       <c r="BS4" t="n">
-        <v>145246081</v>
+        <v>56549393</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B5" t="n">
-        <v>399999</v>
-      </c>
+        <v>45657</v>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>66266666</v>
+        <v>86666665</v>
       </c>
       <c r="D5" t="n">
-        <v>66666665</v>
+        <v>86666665</v>
       </c>
       <c r="E5" t="n">
-        <v>395105757</v>
+        <v>80460087</v>
       </c>
       <c r="F5" t="n">
-        <v>692115997</v>
+        <v>708929299</v>
       </c>
       <c r="G5" t="n">
-        <v>981786611</v>
+        <v>1585081272</v>
       </c>
       <c r="H5" t="n">
-        <v>1641799444</v>
+        <v>2297370899</v>
       </c>
       <c r="I5" t="n">
-        <v>395555983</v>
+        <v>612999530</v>
       </c>
       <c r="J5" t="n">
-        <v>981786611</v>
+        <v>1585081272</v>
       </c>
       <c r="K5" t="n">
-        <v>33005882</v>
+        <v>17786093</v>
       </c>
       <c r="L5" t="n">
-        <v>982689329</v>
+        <v>1606227693</v>
       </c>
       <c r="M5" t="n">
-        <v>1394555907</v>
+        <v>1857380297</v>
       </c>
       <c r="N5" t="n">
-        <v>982895892</v>
+        <v>1600033352</v>
       </c>
       <c r="O5" t="n">
-        <v>206563</v>
+        <v>-6194341</v>
       </c>
       <c r="P5" t="n">
-        <v>982689329</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1715000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1136135</v>
-      </c>
+        <v>1606227693</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>373801465</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
+        <v>184282212</v>
+      </c>
+      <c r="T5" t="n">
+        <v>419999979</v>
+      </c>
       <c r="U5" t="n">
-        <v>500000000</v>
+        <v>866666650</v>
       </c>
       <c r="V5" t="n">
-        <v>500000000</v>
+        <v>866666650</v>
       </c>
       <c r="W5" t="n">
-        <v>887221889</v>
+        <v>958566909</v>
       </c>
       <c r="X5" t="n">
-        <v>481314874</v>
+        <v>302813464</v>
       </c>
       <c r="Y5" t="n">
-        <v>42244799</v>
+        <v>41452198</v>
       </c>
       <c r="Z5" t="n">
-        <v>439070075</v>
+        <v>261361266</v>
       </c>
       <c r="AA5" t="n">
-        <v>27203497</v>
+        <v>10208662</v>
       </c>
       <c r="AB5" t="n">
-        <v>411866578</v>
+        <v>251152604</v>
       </c>
       <c r="AC5" t="n">
-        <v>405907015</v>
+        <v>655753445</v>
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>6752605</v>
+        <v>19910229</v>
       </c>
       <c r="AF5" t="n">
-        <v>253045922</v>
+        <v>447568033</v>
       </c>
       <c r="AG5" t="n">
-        <v>5802385</v>
+        <v>7577431</v>
       </c>
       <c r="AH5" t="n">
-        <v>247243537</v>
+        <v>439990602</v>
       </c>
       <c r="AI5" t="n">
-        <v>29197847</v>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
+        <v>21114766</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>10000000</v>
+      </c>
       <c r="AK5" t="n">
-        <v>99152436</v>
+        <v>152861694</v>
       </c>
       <c r="AL5" t="n">
-        <v>2721989</v>
+        <v>6896459</v>
       </c>
       <c r="AM5" t="n">
-        <v>7103209</v>
+        <v>1316353</v>
       </c>
       <c r="AN5" t="n">
-        <v>89327238</v>
+        <v>144648882</v>
       </c>
       <c r="AO5" t="n">
-        <v>1870117781</v>
+        <v>2558600261</v>
       </c>
       <c r="AP5" t="n">
-        <v>1068654783</v>
+        <v>1289847286</v>
       </c>
       <c r="AQ5" t="n">
-        <v>902718</v>
+        <v>21146421</v>
       </c>
       <c r="AR5" t="n">
-        <v>902718</v>
+        <v>21146421</v>
       </c>
       <c r="AS5" t="n">
-        <v>1067752065</v>
+        <v>1268700865</v>
       </c>
       <c r="AT5" t="n">
-        <v>-1014422137</v>
+        <v>-1163775276</v>
       </c>
       <c r="AU5" t="n">
-        <v>2082174202</v>
+        <v>2432476141</v>
       </c>
       <c r="AV5" t="n">
-        <v>94546859</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>973205206</v>
-      </c>
+        <v>27621024</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>1602209728</v>
+        <v>1959175041</v>
       </c>
       <c r="AY5" t="n">
-        <v>198061192</v>
+        <v>289554245</v>
       </c>
       <c r="AZ5" t="n">
-        <v>187356423</v>
+        <v>156125831</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>801462998</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>86799480</v>
-      </c>
+        <v>1268752975</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
-        <v>96425130</v>
+        <v>130807653</v>
       </c>
       <c r="BE5" t="n">
-        <v>144017771</v>
+        <v>186367314</v>
       </c>
       <c r="BF5" t="n">
-        <v>-7659481</v>
+        <v>-34432090</v>
       </c>
       <c r="BG5" t="n">
-        <v>41681988</v>
+        <v>51497074</v>
       </c>
       <c r="BH5" t="n">
-        <v>2660375</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>107334889</v>
+        <v>169302330</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1923363</v>
+        <v>2553204</v>
       </c>
       <c r="BK5" t="n">
-        <v>3705382</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>291381361</v>
+        <v>338341685</v>
       </c>
       <c r="BM5" t="n">
-        <v>-15176259</v>
+        <v>-27586026</v>
       </c>
       <c r="BN5" t="n">
-        <v>306557620</v>
+        <v>365927711</v>
       </c>
       <c r="BO5" t="n">
-        <v>264009991</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>5633</v>
-      </c>
+        <v>610683119</v>
+      </c>
+      <c r="BP5" t="inlineStr"/>
       <c r="BQ5" t="n">
-        <v>264004358</v>
-      </c>
-      <c r="BR5" t="inlineStr"/>
+        <v>610683119</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>310629751</v>
+      </c>
       <c r="BS5" t="n">
-        <v>264004358</v>
+        <v>300053368</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>86666665</v>
+      </c>
+      <c r="D6" t="n">
+        <v>86666665</v>
+      </c>
+      <c r="E6" t="n">
+        <v>219065571</v>
+      </c>
+      <c r="F6" t="n">
+        <v>745412700</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1611112898</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2342587309</v>
+      </c>
+      <c r="I6" t="n">
+        <v>487715791</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1611112898</v>
+      </c>
+      <c r="K6" t="n">
+        <v>30994540</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1628169149</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1885275983</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1620738788</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-7430361</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1628169149</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>341502520</v>
+      </c>
+      <c r="T6" t="n">
+        <v>419999979</v>
+      </c>
+      <c r="U6" t="n">
+        <v>866666650</v>
+      </c>
+      <c r="V6" t="n">
+        <v>866666650</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1047516585</v>
+      </c>
+      <c r="X6" t="n">
+        <v>315898712</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>38139995</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>277758717</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>20651883</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>257106834</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>731617873</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>13539869</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>467653983</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>10342657</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>457311326</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>10624873</v>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>230115693</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>8214069</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>221901624</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>2668255373</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1448921709</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>17056251</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>17056251</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1431865458</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-1271470904</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2703336362</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>256377029</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>1981366589</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>292046740</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>173546004</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1219333664</v>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="n">
+        <v>155884477</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>215492407</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-29990549</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>75436938</v>
+      </c>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="n">
+        <v>170046018</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>3708730</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1201034</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>347694427</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-22401518</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>370095945</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>495352589</v>
+      </c>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="n">
+        <v>495352589</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>451719643</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>43632946</v>
       </c>
     </row>
   </sheetData>
@@ -2493,7 +2734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2740,538 +2981,605 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-190219118</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-113493069</v>
-      </c>
-      <c r="D2" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>629999969</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-90213884</v>
-      </c>
-      <c r="G2" t="n">
-        <v>610683119</v>
-      </c>
-      <c r="H2" t="n">
-        <v>56549393</v>
-      </c>
-      <c r="I2" t="n">
-        <v>554133726</v>
-      </c>
-      <c r="J2" t="n">
-        <v>744185195</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>-40906585</v>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
-        <v>629999969</v>
-      </c>
-      <c r="N2" t="n">
-        <v>629999969</v>
-      </c>
-      <c r="O2" t="n">
-        <v>121476306</v>
-      </c>
-      <c r="P2" t="n">
-        <v>204969375</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-83493069</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-113493069</v>
-      </c>
-      <c r="S2" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-90046235</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>-1395518</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-1395518</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-88650717</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>167649</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-88818366</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-100005234</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-9386336</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>30140658</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-36694207</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-195265129</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-11544798</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-43551037</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-22579356</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1932956</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-41976578</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-77546316</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>15367344</v>
-      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>39875583</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>113679014</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>573945</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>113105069</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8054270</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>-167632</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>-57900015</v>
-      </c>
+        <v>10290000</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="n">
+        <v>-364852</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-72094089</v>
+        <v>72962154</v>
       </c>
       <c r="C3" t="n">
-        <v>-91963608</v>
+        <v>-306324210</v>
       </c>
       <c r="D3" t="n">
-        <v>45000000</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
+        <v>258778846</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>-270216670</v>
+        <v>-165712786</v>
       </c>
       <c r="G3" t="n">
-        <v>56549393</v>
+        <v>145246081</v>
       </c>
       <c r="H3" t="n">
-        <v>145246081</v>
+        <v>264004358</v>
       </c>
       <c r="I3" t="n">
-        <v>-88696688</v>
+        <v>-118758277</v>
       </c>
       <c r="J3" t="n">
-        <v>-16761657</v>
+        <v>-192129660</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-33333333</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
+        <v>-75000000</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>27483069</v>
+        <v>-111229660</v>
       </c>
       <c r="P3" t="n">
-        <v>74446677</v>
+        <v>-63684296</v>
       </c>
       <c r="Q3" t="n">
-        <v>-46963608</v>
+        <v>-47545364</v>
       </c>
       <c r="R3" t="n">
-        <v>-91963608</v>
+        <v>-306324210</v>
       </c>
       <c r="S3" t="n">
-        <v>45000000</v>
+        <v>258778846</v>
       </c>
       <c r="T3" t="n">
-        <v>-270057612</v>
+        <v>-165303557</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
-      <c r="X3" t="n">
-        <v>-168750</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-168750</v>
-      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>-269888862</v>
+        <v>-165303557</v>
       </c>
       <c r="AA3" t="n">
-        <v>159058</v>
+        <v>409229</v>
       </c>
       <c r="AB3" t="n">
-        <v>-270047920</v>
+        <v>-165712786</v>
       </c>
       <c r="AC3" t="n">
-        <v>198122581</v>
+        <v>238674940</v>
       </c>
       <c r="AD3" t="n">
-        <v>-13536522</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
+        <v>-8447501</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>-29982448</v>
+        <v>-24660588</v>
       </c>
       <c r="AG3" t="n">
-        <v>181506327</v>
+        <v>-159784418</v>
       </c>
       <c r="AH3" t="n">
-        <v>10688462</v>
+        <v>-6545046</v>
       </c>
       <c r="AI3" t="n">
-        <v>-16965916</v>
+        <v>-7211822</v>
       </c>
       <c r="AJ3" t="n">
-        <v>65252292</v>
+        <v>-10886154</v>
       </c>
       <c r="AK3" t="n">
-        <v>51834472</v>
+        <v>-44951566</v>
       </c>
       <c r="AL3" t="n">
-        <v>32639371</v>
+        <v>-67550605</v>
       </c>
       <c r="AM3" t="n">
-        <v>38057646</v>
+        <v>-22639225</v>
       </c>
       <c r="AN3" t="n">
-        <v>26524499</v>
+        <v>18483106</v>
       </c>
       <c r="AO3" t="n">
-        <v>2640000</v>
+        <v>7860000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-2008741</v>
+        <v>15075210</v>
       </c>
       <c r="AQ3" t="n">
-        <v>103128427</v>
+        <v>100368813</v>
       </c>
       <c r="AR3" t="n">
-        <v>248144</v>
+        <v>845526</v>
       </c>
       <c r="AS3" t="n">
-        <v>102880283</v>
+        <v>99523287</v>
       </c>
       <c r="AT3" t="n">
-        <v>7806146</v>
+        <v>7007279</v>
       </c>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>412321</v>
+        <v>1966544</v>
       </c>
       <c r="AW3" t="n">
-        <v>-77758966</v>
+        <v>285811277</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>72962154</v>
+        <v>-72094089</v>
       </c>
       <c r="C4" t="n">
-        <v>-306324210</v>
+        <v>-91963608</v>
       </c>
       <c r="D4" t="n">
-        <v>258778846</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>45000000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
       <c r="F4" t="n">
-        <v>-165712786</v>
+        <v>-270216670</v>
       </c>
       <c r="G4" t="n">
+        <v>56549393</v>
+      </c>
+      <c r="H4" t="n">
         <v>145246081</v>
       </c>
-      <c r="H4" t="n">
-        <v>264004358</v>
-      </c>
       <c r="I4" t="n">
-        <v>-118758277</v>
+        <v>-88696688</v>
       </c>
       <c r="J4" t="n">
-        <v>-192129660</v>
+        <v>-16761657</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-75000000</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+        <v>-33333333</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
       <c r="O4" t="n">
-        <v>-111229660</v>
+        <v>27483069</v>
       </c>
       <c r="P4" t="n">
-        <v>-63684296</v>
+        <v>74446677</v>
       </c>
       <c r="Q4" t="n">
-        <v>-47545364</v>
+        <v>-46963608</v>
       </c>
       <c r="R4" t="n">
-        <v>-306324210</v>
+        <v>-91963608</v>
       </c>
       <c r="S4" t="n">
-        <v>258778846</v>
+        <v>45000000</v>
       </c>
       <c r="T4" t="n">
-        <v>-165303557</v>
+        <v>-270057612</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>-168750</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-168750</v>
+      </c>
       <c r="Z4" t="n">
-        <v>-165303557</v>
+        <v>-269888862</v>
       </c>
       <c r="AA4" t="n">
-        <v>409229</v>
+        <v>159058</v>
       </c>
       <c r="AB4" t="n">
-        <v>-165712786</v>
+        <v>-270047920</v>
       </c>
       <c r="AC4" t="n">
-        <v>238674940</v>
+        <v>198122581</v>
       </c>
       <c r="AD4" t="n">
-        <v>-8447501</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
+        <v>-13536522</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
       <c r="AF4" t="n">
-        <v>-24660588</v>
+        <v>-29982448</v>
       </c>
       <c r="AG4" t="n">
-        <v>-159784418</v>
+        <v>181506327</v>
       </c>
       <c r="AH4" t="n">
-        <v>-6545046</v>
+        <v>10688462</v>
       </c>
       <c r="AI4" t="n">
-        <v>-7211822</v>
+        <v>-16965916</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-10886154</v>
+        <v>65252292</v>
       </c>
       <c r="AK4" t="n">
-        <v>-44951566</v>
+        <v>51834472</v>
       </c>
       <c r="AL4" t="n">
-        <v>-67550605</v>
+        <v>32639371</v>
       </c>
       <c r="AM4" t="n">
-        <v>-22639225</v>
+        <v>38057646</v>
       </c>
       <c r="AN4" t="n">
-        <v>18483106</v>
+        <v>26524499</v>
       </c>
       <c r="AO4" t="n">
-        <v>7860000</v>
+        <v>2640000</v>
       </c>
       <c r="AP4" t="n">
-        <v>15075210</v>
+        <v>-2008741</v>
       </c>
       <c r="AQ4" t="n">
-        <v>100368813</v>
+        <v>103128427</v>
       </c>
       <c r="AR4" t="n">
-        <v>845526</v>
+        <v>248144</v>
       </c>
       <c r="AS4" t="n">
-        <v>99523287</v>
+        <v>102880283</v>
       </c>
       <c r="AT4" t="n">
-        <v>7007279</v>
+        <v>7806146</v>
       </c>
       <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>1966544</v>
+        <v>412321</v>
       </c>
       <c r="AW4" t="n">
-        <v>285811277</v>
+        <v>-77758966</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>187311441</v>
+        <v>-190219118</v>
       </c>
       <c r="C5" t="n">
-        <v>-235925929</v>
+        <v>-113493069</v>
       </c>
       <c r="D5" t="n">
-        <v>301600359</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>30000000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>629999969</v>
+      </c>
       <c r="F5" t="n">
-        <v>-63990301</v>
+        <v>-90213884</v>
       </c>
       <c r="G5" t="n">
-        <v>264004358</v>
+        <v>610683119</v>
       </c>
       <c r="H5" t="n">
-        <v>45455272</v>
+        <v>56549393</v>
       </c>
       <c r="I5" t="n">
-        <v>218549086</v>
+        <v>554133726</v>
       </c>
       <c r="J5" t="n">
-        <v>24954758</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-40906585</v>
-      </c>
+        <v>744185195</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>629999969</v>
+      </c>
+      <c r="N5" t="n">
+        <v>629999969</v>
+      </c>
       <c r="O5" t="n">
-        <v>76794233</v>
+        <v>121476306</v>
       </c>
       <c r="P5" t="n">
-        <v>11119803</v>
+        <v>204969375</v>
       </c>
       <c r="Q5" t="n">
-        <v>65674430</v>
+        <v>-83493069</v>
       </c>
       <c r="R5" t="n">
-        <v>-235925929</v>
+        <v>-113493069</v>
       </c>
       <c r="S5" t="n">
-        <v>301600359</v>
+        <v>30000000</v>
       </c>
       <c r="T5" t="n">
-        <v>-57707414</v>
-      </c>
-      <c r="U5" t="n">
+        <v>-90046235</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="n">
+        <v>-1395518</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-1395518</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-88650717</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>167649</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-88818366</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-100005234</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-9386336</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>30140658</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-36694207</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-195265129</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-11544798</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-43551037</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-20297021</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-349379</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-41976578</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-77546316</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>15367344</v>
+      </c>
+      <c r="AO5" t="n">
         <v>0</v>
       </c>
-      <c r="V5" t="n">
+      <c r="AP5" t="n">
+        <v>39875583</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>113679014</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>573945</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>113105069</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>8054270</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="n">
+        <v>-167632</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-57900015</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-118906669</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-129135961</v>
+      </c>
+      <c r="D6" t="n">
+        <v>120672927</v>
+      </c>
+      <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="W5" t="n">
+      <c r="F6" t="n">
+        <v>-241985751</v>
+      </c>
+      <c r="G6" t="n">
+        <v>495352589</v>
+      </c>
+      <c r="H6" t="n">
+        <v>610683119</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-115330530</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3535270</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="n">
-        <v>-57707414</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>6282887</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-63990301</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>251301742</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-4898220</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="n">
-        <v>-14272262</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-84719600</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>4663376</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-25483154</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>34423044</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-2019693</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>17659960</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-113963133</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>8079467</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>10290000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>14119716</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>99211038</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="n">
-        <v>99211038</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>8446876</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>-364852</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-5011646</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>227824133</v>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>18550910</v>
+      </c>
+      <c r="P6" t="n">
+        <v>27013944</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-8463034</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-129135961</v>
+      </c>
+      <c r="S6" t="n">
+        <v>120672927</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-241944882</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>-330326</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-330326</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-241614556</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>40869</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-241655425</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>123079082</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-19806267</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>24538596</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-41146339</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>5573905</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>5350284</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-24741391</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>62798586</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-800058</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-31776278</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-5257238</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>3221854</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="n">
+        <v>-1444319</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>121348031</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4420496</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>116927535</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7609916</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>-35519</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>35639427</v>
       </c>
     </row>
   </sheetData>
@@ -3285,7 +3593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EQ2"/>
+  <dimension ref="A1:ER2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3436,590 +3744,595 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>trailingPE</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>forwardPE</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>regularMarketVolume</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>averageVolume</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>averageVolume10days</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>averageDailyVolume10Day</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ask</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>marketCap</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>nonDilutedMarketCap</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLow</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>allTimeHigh</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>allTimeLow</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>fiftyDayAverage</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>twoHundredDayAverage</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendRate</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendYield</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>tradeable</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>enterpriseValue</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>profitMargins</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>floatShares</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>sharesOutstanding</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>heldPercentInsiders</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>heldPercentInstitutions</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>impliedSharesOutstanding</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>bookValue</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>lastFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>nextFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>mostRecentQuarter</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>netIncomeToCommon</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>trailingEps</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>forwardEps</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>lastSplitFactor</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>lastSplitDate</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>enterpriseToRevenue</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>enterpriseToEbitda</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>52WeekChange</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>SandP52WeekChange</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>lastDividendValue</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>lastDividendDate</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>quoteType</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>currentPrice</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>targetHighPrice</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>targetLowPrice</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>targetMeanPrice</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>targetMedianPrice</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>recommendationKey</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>numberOfAnalystOpinions</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>totalCash</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>totalCashPerShare</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>totalDebt</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>quickRatio</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>currentRatio</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>totalRevenue</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>debtToEquity</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>revenuePerShare</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>returnOnAssets</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>returnOnEquity</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>grossProfits</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>freeCashflow</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>operatingCashflow</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4041,10 +4354,8 @@
           <t>Jeddah</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>23326</t>
-        </is>
+      <c r="D2" t="n">
+        <v>23326</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4116,28 +4427,28 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>19.45</v>
+        <v>18.35</v>
       </c>
       <c r="U2" t="n">
-        <v>19.55</v>
+        <v>18.35</v>
       </c>
       <c r="V2" t="n">
-        <v>19.02</v>
+        <v>18.13</v>
       </c>
       <c r="W2" t="n">
-        <v>19.84</v>
+        <v>18.4</v>
       </c>
       <c r="X2" t="n">
-        <v>19.45</v>
+        <v>18.35</v>
       </c>
       <c r="Y2" t="n">
-        <v>19.55</v>
+        <v>18.35</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.02</v>
+        <v>18.13</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.84</v>
+        <v>18.4</v>
       </c>
       <c r="AB2" t="n">
         <v>1688342400</v>
@@ -4146,403 +4457,406 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>74.34614999999999</v>
+        <v>95.89474</v>
       </c>
       <c r="AE2" t="n">
-        <v>1139204</v>
+        <v>70.07692</v>
       </c>
       <c r="AF2" t="n">
-        <v>1139204</v>
+        <v>403689</v>
       </c>
       <c r="AG2" t="n">
-        <v>1126815</v>
+        <v>403689</v>
       </c>
       <c r="AH2" t="n">
-        <v>1134117</v>
+        <v>1145017</v>
       </c>
       <c r="AI2" t="n">
-        <v>1134117</v>
+        <v>596019</v>
       </c>
       <c r="AJ2" t="n">
-        <v>19.25</v>
+        <v>596019</v>
       </c>
       <c r="AK2" t="n">
-        <v>19.36</v>
+        <v>18.13</v>
       </c>
       <c r="AL2" t="n">
-        <v>1675266560</v>
+        <v>18.15</v>
       </c>
       <c r="AM2" t="n">
-        <v>1685666634</v>
+        <v>1579066496</v>
       </c>
       <c r="AN2" t="n">
+        <v>1579066636</v>
+      </c>
+      <c r="AO2" t="n">
         <v>15.7</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AP2" t="n">
         <v>31.52</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AQ2" t="n">
         <v>51</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AR2" t="n">
         <v>7.875</v>
       </c>
-      <c r="AR2" t="n">
-        <v>1.6020076</v>
-      </c>
       <c r="AS2" t="n">
-        <v>17.8722</v>
+        <v>1.5100143</v>
       </c>
       <c r="AT2" t="n">
-        <v>21.8819</v>
+        <v>18.1456</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>21.3018</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
-      <c r="AX2" t="b">
+      <c r="AY2" t="b">
         <v>0</v>
       </c>
-      <c r="AY2" t="n">
-        <v>2267524096</v>
-      </c>
       <c r="AZ2" t="n">
+        <v>2188758016</v>
+      </c>
+      <c r="BA2" t="n">
         <v>0.01538</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BB2" t="n">
         <v>76509935</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BC2" t="n">
         <v>86666665</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BD2" t="n">
         <v>0</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="BE2" t="n">
         <v>0.33326</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="BF2" t="n">
         <v>86666665</v>
       </c>
-      <c r="BF2" t="n">
+      <c r="BG2" t="n">
         <v>16.31</v>
       </c>
-      <c r="BG2" t="n">
-        <v>1.1851625</v>
-      </c>
       <c r="BH2" t="n">
+        <v>1.1171061</v>
+      </c>
+      <c r="BI2" t="n">
         <v>1767139200</v>
       </c>
-      <c r="BI2" t="n">
+      <c r="BJ2" t="n">
         <v>1798675200</v>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BK2" t="n">
         <v>1774915200</v>
       </c>
-      <c r="BK2" t="n">
+      <c r="BL2" t="n">
         <v>16084640</v>
       </c>
-      <c r="BL2" t="n">
-        <v>-0.22</v>
-      </c>
       <c r="BM2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="BN2" t="n">
         <v>0.26</v>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>4:3</t>
         </is>
       </c>
-      <c r="BO2" t="n">
+      <c r="BP2" t="n">
         <v>1669507200</v>
       </c>
-      <c r="BP2" t="n">
-        <v>2.168</v>
-      </c>
       <c r="BQ2" t="n">
-        <v>16.374</v>
+        <v>2.093</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0.30535716</v>
+        <v>15.805</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.27294624</v>
+        <v>-0.2798419</v>
       </c>
       <c r="BT2" t="n">
+        <v>0.2568333</v>
+      </c>
+      <c r="BU2" t="n">
         <v>0.5</v>
       </c>
-      <c r="BU2" t="n">
+      <c r="BV2" t="n">
         <v>1688342400</v>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>EQUITY</t>
         </is>
       </c>
-      <c r="BW2" t="n">
-        <v>19.33</v>
-      </c>
       <c r="BX2" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="BY2" t="n">
         <v>25</v>
       </c>
-      <c r="BY2" t="n">
+      <c r="BZ2" t="n">
         <v>22</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>23.5</v>
       </c>
       <c r="CA2" t="n">
         <v>23.5</v>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CB2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="CC2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="CC2" t="n">
+      <c r="CD2" t="n">
         <v>2</v>
       </c>
-      <c r="CD2" t="n">
+      <c r="CE2" t="n">
         <v>463758528</v>
       </c>
-      <c r="CE2" t="n">
+      <c r="CF2" t="n">
         <v>4.651</v>
       </c>
-      <c r="CF2" t="n">
+      <c r="CG2" t="n">
         <v>138486848</v>
       </c>
-      <c r="CG2" t="n">
+      <c r="CH2" t="n">
         <v>810839168</v>
       </c>
-      <c r="CH2" t="n">
+      <c r="CI2" t="n">
         <v>1.038</v>
       </c>
-      <c r="CI2" t="n">
+      <c r="CJ2" t="n">
         <v>1.513</v>
       </c>
-      <c r="CJ2" t="n">
+      <c r="CK2" t="n">
         <v>1045729472</v>
       </c>
-      <c r="CK2" t="n">
+      <c r="CL2" t="n">
         <v>50.072</v>
       </c>
-      <c r="CL2" t="n">
+      <c r="CM2" t="n">
         <v>11.7</v>
       </c>
-      <c r="CM2" t="n">
+      <c r="CN2" t="n">
         <v>0.0072600003</v>
       </c>
-      <c r="CN2" t="n">
+      <c r="CO2" t="n">
         <v>0.00962</v>
       </c>
-      <c r="CO2" t="n">
+      <c r="CP2" t="n">
         <v>123880280</v>
       </c>
-      <c r="CP2" t="n">
+      <c r="CQ2" t="n">
         <v>-151059664</v>
       </c>
-      <c r="CQ2" t="n">
+      <c r="CR2" t="n">
         <v>132662264</v>
       </c>
-      <c r="CR2" t="n">
+      <c r="CS2" t="n">
         <v>-0.057</v>
       </c>
-      <c r="CS2" t="n">
+      <c r="CT2" t="n">
         <v>0.11846</v>
       </c>
-      <c r="CT2" t="n">
+      <c r="CU2" t="n">
         <v>0.13243</v>
       </c>
-      <c r="CU2" t="n">
+      <c r="CV2" t="n">
         <v>0.01953</v>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="CW2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="CX2" t="inlineStr">
         <is>
           <t>1202.SR</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="CY2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DA2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DB2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="DB2" t="b">
+      <c r="DC2" t="b">
         <v>0</v>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DD2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="DD2" t="b">
+      <c r="DE2" t="n">
+        <v>-0.70845264</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>1603882740</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>107.17647</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0.07439995000000001</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>0.004100165</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>-3.0818005</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>-0.14467324</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DR2" t="b">
         <v>0</v>
       </c>
-      <c r="DE2" t="n">
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>Middle East Paper Co.</t>
+        </is>
+      </c>
+      <c r="DT2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="n">
         <v>1450681200000</v>
       </c>
-      <c r="DF2" t="n">
-        <v>-0.12000084</v>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>19.02 - 19.84</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DV2" t="n">
+        <v>-0.13000107</v>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>18.13 - 18.4</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
         <is>
           <t>Saudi</t>
         </is>
       </c>
-      <c r="DI2" t="n">
-        <v>1126815</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>0.2312102</v>
-      </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DY2" t="n">
+        <v>1145017</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>2.5199995</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0.16050953</v>
+      </c>
+      <c r="EB2" t="inlineStr">
         <is>
           <t>15.7 - 31.52</t>
         </is>
       </c>
-      <c r="DM2" t="n">
-        <v>-12.190001</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>-0.3867386</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>-30.535715</v>
-      </c>
-      <c r="DP2" t="n">
+      <c r="EC2" t="n">
+        <v>-13.300001</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>-0.42195433</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-27.98419</v>
+      </c>
+      <c r="EF2" t="n">
         <v>1603882740</v>
       </c>
-      <c r="DQ2" t="n">
-        <v>1603882740</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>113.70588</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>1.4577999</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.08156802</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-2.5519009</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.11662153</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.6169709</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>19.33</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EH2" t="n">
+        <v>1781784966</v>
+      </c>
+      <c r="EI2" t="inlineStr">
         <is>
           <t>SAU</t>
         </is>
       </c>
-      <c r="EF2" t="inlineStr">
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>finmb_252657147</t>
         </is>
       </c>
-      <c r="EG2" t="inlineStr">
+      <c r="EK2" t="inlineStr">
         <is>
           <t>Asia/Riyadh</t>
         </is>
       </c>
-      <c r="EH2" t="inlineStr">
+      <c r="EL2" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="EI2" t="n">
+      <c r="EM2" t="n">
         <v>10800000</v>
       </c>
-      <c r="EJ2" t="inlineStr">
+      <c r="EN2" t="inlineStr">
         <is>
           <t>sr_market</t>
         </is>
       </c>
-      <c r="EK2" t="b">
+      <c r="EO2" t="b">
         <v>0</v>
       </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EM2" t="n">
-        <v>1780402593</v>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>Middle East Paper Co.</t>
-        </is>
-      </c>
-      <c r="EO2" t="inlineStr">
+      <c r="EP2" t="inlineStr">
         <is>
           <t>Middle East Company for Manufacturing and Producing Paper</t>
         </is>
       </c>
-      <c r="EP2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EQ2" t="inlineStr"/>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="ER2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
